--- a/reports/findings.xlsx
+++ b/reports/findings.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,11 +35,8 @@
       <b val="1"/>
       <color rgb="00ffffff"/>
     </font>
-    <font>
-      <color rgb="00065f46"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +47,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00374151"/>
         <bgColor rgb="00374151"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00d1fae5"/>
-        <bgColor rgb="00d1fae5"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,16 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -451,13 +439,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
@@ -513,17 +501,17 @@
           <t>Gitleaks</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Repository History</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>No hardcoded secrets detected</t>
         </is>
@@ -545,86 +533,22 @@
           <t>Semgrep</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Backend Modules</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>FastAPI static analysis passed successfully</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>VERIFIED CLEAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>SEC-003</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Trivy</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Docker Filesystem</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Filesystem scanned clean</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>VERIFIED CLEAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>SEC-004</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Dependency Audit</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>requirements.txt / package.json</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>No blocked third-party dependencies</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>VERIFIED CLEAN</t>
         </is>

--- a/reports/findings.xlsx
+++ b/reports/findings.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Security Findings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,28 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Outfit"/>
       <b val="1"/>
-      <color rgb="00ef4444"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00ffffff"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00374151"/>
-        <bgColor rgb="00374151"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -62,18 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,125 +417,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OrbitX Consolidated DevSecOps Security Findings</t>
+          <t>ID</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Finding ID</t>
+          <t>Tool</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Tool / Source</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>File Path / Target</t>
+          <t>Target</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Vulnerability Details</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Remediation Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>SEC-001</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Gitleaks</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Repository History</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>No hardcoded secrets detected</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>VERIFIED CLEAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>SEC-002</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Semgrep</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Backend Modules</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>FastAPI static analysis passed successfully</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>VERIFIED CLEAN</t>
+          <t>Status</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>